--- a/output/graficos_dimensiones/comunal_o_ocup_a_2021_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2021_magallanes.xlsx
@@ -60,12 +60,12 @@
     <t xml:space="preserve">San Gregorio</t>
   </si>
   <si>
+    <t xml:space="preserve">Timaukel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Río Verde</t>
   </si>
   <si>
-    <t xml:space="preserve">Timaukel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:52</t>
+    <t xml:space="preserve">2026-09-09 22:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -629,7 +629,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>12103</v>
+        <v>12303</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -642,7 +642,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>12303</v>
+        <v>12103</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2021_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2021_magallanes.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:41</t>
+    <t xml:space="preserve">2026-09-18 10:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2021_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2021_magallanes.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comunas'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comunas'!$A$1:$E$12</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -51,21 +51,24 @@
     <t xml:space="preserve">Cabo de Hornos</t>
   </si>
   <si>
+    <t xml:space="preserve">Río Verde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Gregorio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antártica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primavera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timaukel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Torres del Paine</t>
   </si>
   <si>
-    <t xml:space="preserve">Primavera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Gregorio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timaukel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Verde</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -75,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:03</t>
+    <t xml:space="preserve">2026-09-23 12:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -590,9 +593,11 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>12402</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>12103</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
@@ -603,9 +608,11 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>12302</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>12104</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
@@ -616,9 +623,11 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>12104</v>
-      </c>
-      <c r="D9" s="2"/>
+        <v>12202</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
@@ -629,9 +638,11 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>12303</v>
-      </c>
-      <c r="D10" s="2"/>
+        <v>12302</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
@@ -642,13 +653,30 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>12103</v>
-      </c>
-      <c r="D11" s="2"/>
+        <v>12303</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E11" s="2"/>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>12402</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:E12"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -665,50 +693,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -716,15 +744,15 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2021_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2021_magallanes.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:09</t>
+    <t xml:space="preserve">2026-10-02 13:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2021_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2021_magallanes.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:42</t>
+    <t xml:space="preserve">2026-10-05 08:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
